--- a/nomination_forms/015_employee_appreciation_message_form--nomination_forms.xlsx
+++ b/nomination_forms/015_employee_appreciation_message_form--nomination_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_smith',_'value':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Smith', 'value': 'bob_smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_smith',_'value':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Smith', 'value': 'bob_smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team Lead', 'value': 'team_lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager', 'value': 'manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'director',_'value':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Director', 'value': 'director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'ceo',_'value':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'CEO', 'value': 'ceo'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'send_a_thank_you_note',_'value':_'send_a_thank_you_note'}</t>
+          <t>send_a_thank_you_note</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Send a thank you note', 'value': 'send_a_thank_you_note'}</t>
+          <t>Send a thank you note</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'meet_with_the_team_lead',_'value':_'meet_with_team_lead'}</t>
+          <t>meet_with_the_team_lead</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Meet with the team lead', 'value': 'meet_with_team_lead'}</t>
+          <t>Meet with the team lead</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'review_and_follow_up_in_1_month',_'value':_'review_and_follow_up_in_1_month'}</t>
+          <t>review_and_follow_up_in_1_month</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Review and follow up in 1 month', 'value': 'review_and_follow_up_in_1_month'}</t>
+          <t>Review and follow up in 1 month</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'review_and_follow_up_in_3_months',_'value':_'review_and_follow_up_in_3_months'}</t>
+          <t>review_and_follow_up_in_3_months</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Review and follow up in 3 months', 'value': 'review_and_follow_up_in_3_months'}</t>
+          <t>Review and follow up in 3 months</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'review_and_follow_up_in_6_months',_'value':_'review_and_follow_up_in_6_months'}</t>
+          <t>review_and_follow_up_in_6_months</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Review and follow up in 6 months', 'value': 'review_and_follow_up_in_6_months'}</t>
+          <t>Review and follow up in 6 months</t>
         </is>
       </c>
     </row>
